--- a/course-design-2/outputs/tables/ch3/20_modeling_dataset_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/20_modeling_dataset_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_总体结构" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_字段清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Feature_Manifest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_目标泄漏黑名单" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_缺失值统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能特征候选" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_类别特征基数" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_模型样本筛选" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_一岗一行检查" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_数据集版本信息" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_技能口径控制" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_门禁" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="01_总体结构" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_字段清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_Feature_Manifest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_目标泄漏黑名单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_缺失值统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_技能特征候选" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_类别特征基数" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_模型样本筛选" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_一岗一行检查" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="11_数据集版本信息" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="12_技能统计范围控制" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="10_门禁" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -644,7 +644,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:38:32</t>
+          <t>2026-10-09 13:47:10</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c3f6c3e</t>
+          <t>81d8c0e</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>技能口径</t>
+          <t>技能统计范围</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>技能口径 = ALL_USABLE</t>
+          <t>技能统计范围 = ALL_USABLE</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>是否参与模型（分析集口径）</t>
+          <t>是否参与模型（分析集范围）</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>ALL_USABLE 口径规范技能集合（关系引用）</t>
+          <t>ALL_USABLE 统计范围规范技能集合（关系引用）</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>技能提取口径控制变量（REQUIREMENT_SECTION / FULL_TEXT_FALLBACK / EMPTY_TEXT）</t>
+          <t>技能提取统计范围控制变量（REQUIREMENT_SECTION / FULL_TEXT_FALLBACK / EMPTY_TEXT）</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>技能口径 = ALL_USABLE；建模样本 14883 行；EMPTY_TEXT 不解释为「无技能」，由文本是否为空/技能提取范围显式控制</t>
+          <t>技能统计范围 = ALL_USABLE；建模样本 14883 行；EMPTY_TEXT 不解释为「无技能」，由文本是否为空/技能提取范围显式控制</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>阈值口径</t>
+          <t>阈值设定</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
     </row>

--- a/course-design-2/outputs/tables/ch3/20_modeling_dataset_audit.xlsx
+++ b/course-design-2/outputs/tables/ch3/20_modeling_dataset_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_总体结构" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_字段清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_Feature_Manifest" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_目标泄漏黑名单" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_缺失值统计" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_技能特征候选" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_类别特征基数" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_模型样本筛选" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_一岗一行检查" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="11_数据集版本信息" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="12_技能统计范围控制" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="10_门禁" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_总体结构" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_字段清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Feature_Manifest" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_目标泄漏黑名单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_缺失值统计" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_技能特征候选" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_类别特征基数" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_模型样本筛选" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_一岗一行检查" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_数据集版本信息" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_技能统计范围控制" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_门禁" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -542,7 +542,6 @@
       <c r="B7" t="n">
         <v>21</v>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,7 +552,6 @@
       <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -564,7 +562,6 @@
       <c r="B9" t="n">
         <v>19</v>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -575,7 +572,6 @@
       <c r="B10" t="n">
         <v>19</v>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -586,7 +582,6 @@
       <c r="B11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -597,7 +592,6 @@
       <c r="B12" t="n">
         <v>6</v>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -608,7 +602,6 @@
       <c r="B13" t="n">
         <v>54</v>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -644,7 +637,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-09 13:47:10</t>
+          <t>2026-09-16 15:38:32</t>
         </is>
       </c>
     </row>
@@ -656,7 +649,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81d8c0e</t>
+          <t>c3f6c3e</t>
         </is>
       </c>
     </row>
@@ -735,7 +728,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>技能统计范围</t>
+          <t>技能口径</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -852,7 +845,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>技能统计范围 = ALL_USABLE</t>
+          <t>技能口径 = ALL_USABLE</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2596,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2713,7 +2705,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2880,7 +2871,6 @@
           <t>OneHotEncoder(handle_unknown=ignore)；缺失编码为「未知」</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2933,7 +2923,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2986,7 +2975,6 @@
           <t>OneHotEncoder(handle_unknown=ignore)；缺失编码为「未知」</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3039,7 +3027,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3149,7 +3136,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3202,7 +3188,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3255,7 +3240,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3365,7 +3349,6 @@
           <t>OneHotEncoder(handle_unknown=ignore)；缺失编码为「未知」</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3418,7 +3401,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3528,7 +3510,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3581,7 +3562,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3634,7 +3614,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3858,7 +3837,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4025,7 +4003,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4078,7 +4055,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4131,7 +4107,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4184,7 +4159,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4294,7 +4268,6 @@
           <t>OneHotEncoder(handle_unknown=ignore)；缺失编码为「未知」</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4461,7 +4434,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4514,7 +4486,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4567,7 +4538,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4620,7 +4590,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4673,7 +4642,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4840,7 +4808,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4893,7 +4860,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4948,7 +4914,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>ALL_USABLE 统计范围规范技能集合（关系引用）</t>
+          <t>ALL_USABLE 口径规范技能集合（关系引用）</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5083,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5170,7 +5135,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5223,7 +5187,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5276,7 +5239,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5329,7 +5291,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5382,7 +5343,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5435,7 +5395,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5488,7 +5447,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5541,7 +5499,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5594,7 +5551,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5647,7 +5603,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5700,7 +5655,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5755,7 +5709,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>技能提取统计范围控制变量（REQUIREMENT_SECTION / FULL_TEXT_FALLBACK / EMPTY_TEXT）</t>
+          <t>技能提取口径控制变量（REQUIREMENT_SECTION / FULL_TEXT_FALLBACK / EMPTY_TEXT）</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5821,6 @@
           <t>中位数填补 + 必要时缺失指示；线性模型 StandardScaler</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6264,7 +6217,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>技能统计范围 = ALL_USABLE；建模样本 14883 行；EMPTY_TEXT 不解释为「无技能」，由文本是否为空/技能提取范围显式控制</t>
+          <t>技能口径 = ALL_USABLE；建模样本 14883 行；EMPTY_TEXT 不解释为「无技能」，由文本是否为空/技能提取范围显式控制</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8811,6 @@
           <t>1 intern_id = 1 行</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8874,7 +8826,6 @@
           <t>是否面议 = 1（正式目标不可用，仍保留在全量分析集）</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8890,7 +8841,6 @@
           <t>薪资解析状态 ≠ 已解析 或 薪资中点为空</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8906,7 +8856,6 @@
           <t>薪资异常标志 非空（下限非正数 / 上下限倒置 / 上限非正数）</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
